--- a/Financial Analysis/HAG.xlsx
+++ b/Financial Analysis/HAG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA82E7B-0879-442C-986A-77CE439341F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4907921A-3E0A-42F8-9B75-10044241E54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9844EE4C-2224-4280-A447-ECC8157A654B}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="62">
   <si>
     <t>HAG</t>
   </si>
@@ -203,16 +203,26 @@
   </si>
   <si>
     <t>Heavily overvalued</t>
+  </si>
+  <si>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$€-2]\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,6 +253,15 @@
     </font>
     <font>
       <i/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -291,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -310,6 +329,9 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -764,7 +786,7 @@
       </c>
       <c r="F3" s="6">
         <f ca="1">TODAY()</f>
-        <v>45925</v>
+        <v>45933</v>
       </c>
       <c r="G3" s="6">
         <v>45968</v>
@@ -839,7 +861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F13486D-291F-4206-A816-423EAA893757}">
-  <dimension ref="B2:EJ56"/>
+  <dimension ref="B2:EJ60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -5338,6 +5360,36 @@
         <v>58</v>
       </c>
     </row>
+    <row r="57" spans="2:35" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="J57" s="13">
+        <v>4696</v>
+      </c>
+      <c r="K57" s="13"/>
+      <c r="L57" s="13">
+        <v>4649</v>
+      </c>
+    </row>
+    <row r="59" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="B59" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L59" s="14">
+        <f>Main!D9/Model!L57</f>
+        <v>2.6322219832221987</v>
+      </c>
+    </row>
+    <row r="60" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="B60" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L60" s="10">
+        <f>L57/Main!D9-1</f>
+        <v>-0.62009283169352469</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
